--- a/Data Files/12.3. Reverse Credit Transfer - Failed - Duplicate Transaction.xlsx
+++ b/Data Files/12.3. Reverse Credit Transfer - Failed - Duplicate Transaction.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chindy\Chindy\BIFAST\Revamp\Komi-API Now\Komi-API\Data Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chindy\Chindy\BIFAST\Revamp\Automation\Komi-API BIFAST 2.0\Komi-API Now\Komi-API\Data Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBF444A-FADF-4E1B-A16D-9B1F451A9B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597C8615-1AB0-4969-8CF6-E40072FDBBAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E8FF007-8F4D-4B7A-B8E2-B73F1FC7F786}"/>
   </bookViews>
@@ -34,199 +34,208 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="62">
-  <si>
-    <t>Authorization</t>
-  </si>
-  <si>
-    <t>ContentType</t>
-  </si>
-  <si>
-    <t>requestID</t>
-  </si>
-  <si>
-    <t>requestDate</t>
-  </si>
-  <si>
-    <t>numberOfTrx</t>
-  </si>
-  <si>
-    <t>settlementMethod</t>
-  </si>
-  <si>
-    <t>endToEndID</t>
-  </si>
-  <si>
-    <t>transactionID</t>
-  </si>
-  <si>
-    <t>channelType</t>
-  </si>
-  <si>
-    <t>transactionPurpose</t>
-  </si>
-  <si>
-    <t>settlementAmount</t>
-  </si>
-  <si>
-    <t>settlementCurrency</t>
-  </si>
-  <si>
-    <t>settlementDate</t>
-  </si>
-  <si>
-    <t>chargeBearer</t>
-  </si>
-  <si>
-    <t>originatingBIC</t>
-  </si>
-  <si>
-    <t>receivingBIC</t>
-  </si>
-  <si>
-    <t>paymentInfo</t>
-  </si>
-  <si>
-    <t>relatedEndToEndID</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>natID</t>
-  </si>
-  <si>
-    <t>accountID</t>
-  </si>
-  <si>
-    <t>accountType</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>rsdntSts</t>
-  </si>
-  <si>
-    <t>twnNm</t>
-  </si>
-  <si>
-    <t>namecreditor</t>
-  </si>
-  <si>
-    <t>natIDcreditor</t>
-  </si>
-  <si>
-    <t>accountIDcreditor</t>
-  </si>
-  <si>
-    <t>accountTypecreditor</t>
-  </si>
-  <si>
-    <t>proxyTypecreditor</t>
-  </si>
-  <si>
-    <t>proxyValuecreditor</t>
-  </si>
-  <si>
-    <t>typecreditor</t>
-  </si>
-  <si>
-    <t>rsdntStscreditor</t>
-  </si>
-  <si>
-    <t>twnNmcreditor</t>
-  </si>
-  <si>
-    <t>application/json</t>
-  </si>
-  <si>
-    <t>20230727APIBANK101110002036</t>
-  </si>
-  <si>
-    <t>2023-07-27T07:57:55.516</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
   <si>
     <t>CLRG</t>
   </si>
   <si>
-    <t>20230727APIBANK1011O0110002036</t>
-  </si>
-  <si>
     <t>01</t>
   </si>
   <si>
-    <t>01101</t>
-  </si>
-  <si>
-    <t>11005.01</t>
-  </si>
-  <si>
     <t>IDR</t>
   </si>
   <si>
-    <t>2023-07-27</t>
-  </si>
-  <si>
     <t>DEBT</t>
   </si>
   <si>
-    <t>APIBANK1</t>
-  </si>
-  <si>
-    <t>APIBANK4</t>
-  </si>
-  <si>
-    <t>Payment for housing</t>
-  </si>
-  <si>
-    <t>20230727APIBANK1010O0110019935</t>
-  </si>
-  <si>
-    <t>NUR SYIFAUN NAS</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>1234567891011121</t>
-  </si>
-  <si>
     <t>SVGS</t>
   </si>
   <si>
-    <t>0300</t>
-  </si>
-  <si>
-    <t>YUNAN LASITO</t>
-  </si>
-  <si>
-    <t>0102030405060708</t>
-  </si>
-  <si>
     <t>400000001</t>
   </si>
   <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>john.smith@example.com</t>
-  </si>
-  <si>
-    <t>Basic QWRtaW5pc3RyYXRvcjptYW5hZ2U=</t>
-  </si>
-  <si>
-    <t>20230726APIBANK15100100008109</t>
+    <t>AppHdrId</t>
+  </si>
+  <si>
+    <t>ToId</t>
+  </si>
+  <si>
+    <t>BizMsgIdr</t>
+  </si>
+  <si>
+    <t>MsgDefIdr</t>
+  </si>
+  <si>
+    <t>CreDt</t>
+  </si>
+  <si>
+    <t>GrpHdrCreDtTm</t>
+  </si>
+  <si>
+    <t>GrpHdrMsgId</t>
+  </si>
+  <si>
+    <t>GrpHdrNbOfTxs</t>
+  </si>
+  <si>
+    <t>SttlmInfSttlmMtd</t>
+  </si>
+  <si>
+    <t>PmtIdEndToEndId</t>
+  </si>
+  <si>
+    <t>PmtIdTxId</t>
+  </si>
+  <si>
+    <t>ClrSysRef</t>
+  </si>
+  <si>
+    <t>LclInstrmPrtry</t>
+  </si>
+  <si>
+    <t>CtgyPurpPrtry</t>
+  </si>
+  <si>
+    <t>IntrBkSttlmDt</t>
+  </si>
+  <si>
+    <t>ChrgBr</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Ccy</t>
+  </si>
+  <si>
+    <t>DbtrNm</t>
+  </si>
+  <si>
+    <t>OrgIdId</t>
+  </si>
+  <si>
+    <t>DbtrAcctId</t>
+  </si>
+  <si>
+    <t>TpPrtry</t>
+  </si>
+  <si>
+    <t>DbtrAgtId</t>
+  </si>
+  <si>
+    <t>CdtrAgtId</t>
+  </si>
+  <si>
+    <t>CdtrNm</t>
+  </si>
+  <si>
+    <t>PrvtIdId</t>
+  </si>
+  <si>
+    <t>CdtrAcctOthrId</t>
+  </si>
+  <si>
+    <t>CdtrAcctTpPrtry</t>
+  </si>
+  <si>
+    <t>RmtInfUstrd</t>
+  </si>
+  <si>
+    <t>EnvlpRsdntSts</t>
+  </si>
+  <si>
+    <t>EnvlpTwnNm</t>
+  </si>
+  <si>
+    <t>CdtrTp</t>
+  </si>
+  <si>
+    <t>CdtrRsdntSts</t>
+  </si>
+  <si>
+    <t>CdtrTwnNm</t>
+  </si>
+  <si>
+    <t>RltdEndToEndId</t>
+  </si>
+  <si>
+    <t>FASTIDJA</t>
+  </si>
+  <si>
+    <t>ATOSIDJ1</t>
+  </si>
+  <si>
+    <t>20250807FASTIDJA011H9920100108</t>
+  </si>
+  <si>
+    <t>pacs.008.001.08</t>
+  </si>
+  <si>
+    <t>2025-08-07T03:21:33Z</t>
+  </si>
+  <si>
+    <t>2025-08-07T10:21:23.050</t>
+  </si>
+  <si>
+    <t>20250807FASTIDJA011361528</t>
+  </si>
+  <si>
+    <t>20250807BMRIIDJA011O99011008</t>
+  </si>
+  <si>
+    <t>20250807PDJBIDJA110O01910008</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>01199</t>
+  </si>
+  <si>
+    <t>2025-08-07</t>
+  </si>
+  <si>
+    <t>1196</t>
+  </si>
+  <si>
+    <t>KU000022000462138</t>
+  </si>
+  <si>
+    <t>981442049202000</t>
+  </si>
+  <si>
+    <t>BMRIIDJA</t>
+  </si>
+  <si>
+    <t>ANDRY SYAPUTRA</t>
+  </si>
+  <si>
+    <t>0019845621100</t>
+  </si>
+  <si>
+    <t>Test transfer</t>
+  </si>
+  <si>
+    <t>0191</t>
+  </si>
+  <si>
+    <t>0294</t>
+  </si>
+  <si>
+    <t>20230728APIBANK1010O0100000121</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,16 +243,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -253,6 +254,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -305,9 +312,8 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -317,10 +323,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -633,257 +638,241 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B04F1129-82C3-4392-B448-C815D8702692}">
-  <dimension ref="A1:AH2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AI2"/>
+  <sheetFormatPr defaultColWidth="14.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="32.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.5546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="10.33203125" customWidth="1"/>
+    <col min="3" max="3" width="32.44140625" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" customWidth="1"/>
+    <col min="7" max="7" width="29.109375" customWidth="1"/>
+    <col min="8" max="8" width="8.44140625" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" customWidth="1"/>
+    <col min="10" max="10" width="31.33203125" customWidth="1"/>
+    <col min="11" max="11" width="28.88671875" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="19" max="19" width="19.6640625" customWidth="1"/>
+    <col min="20" max="20" width="22.88671875" customWidth="1"/>
+    <col min="25" max="25" width="18.33203125" customWidth="1"/>
+    <col min="28" max="28" width="18.77734375" customWidth="1"/>
+    <col min="35" max="35" width="32.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2" s="3">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="J2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD2" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE2" s="7" t="s">
-        <v>59</v>
+      <c r="AE2" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="AF2" s="4" t="s">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="AG2" s="4" t="s">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="AH2" s="4" t="s">
-        <v>54</v>
+        <v>63</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="AE2" r:id="rId1" xr:uid="{3BA41114-D52D-4E29-BC21-787F64426E93}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>